--- a/BDD_standard_format/excel/canada_standard.xlsx
+++ b/BDD_standard_format/excel/canada_standard.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,30 +455,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>taille_colis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>poids_kg</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>prix_livraison_eur</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>statut_colis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>delai_livraison</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>relation_livreur</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>etat_colis</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>service_client</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>satisfaction_globale</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>commentaire_global</t>
         </is>
@@ -503,16 +528,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4.53</v>
+      </c>
       <c r="H2" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>9</v>
       </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,16 +579,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1.26</v>
+      </c>
       <c r="H3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,16 +630,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H4" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="N4" t="n">
         <v>6</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -593,16 +681,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H5" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>7</v>
       </c>
-      <c r="I5" t="n">
+      <c r="N5" t="n">
         <v>8</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -623,16 +732,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2.42</v>
+      </c>
       <c r="H6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -653,16 +783,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H7" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="N7" t="n">
         <v>9</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,16 +834,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.91</v>
+      </c>
       <c r="H8" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
+      <c r="N8" t="n">
         <v>9</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -713,16 +885,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4.86</v>
+      </c>
       <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="I9" t="n">
+      <c r="N9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,16 +936,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4.14</v>
+      </c>
       <c r="H10" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="N10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -773,16 +987,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1.23</v>
+      </c>
       <c r="H11" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="N11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -803,16 +1038,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3.75</v>
+      </c>
       <c r="H12" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
         <v>8</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -833,16 +1089,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.22</v>
+      </c>
       <c r="H13" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="N13" t="n">
         <v>9</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -863,16 +1140,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.44</v>
+      </c>
       <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="N14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,16 +1191,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>8.09</v>
+      </c>
       <c r="H15" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="N15" t="n">
         <v>8</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -923,16 +1242,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1.45</v>
+      </c>
       <c r="H16" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="N16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -953,16 +1293,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.87</v>
+      </c>
       <c r="H17" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="n">
+      <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -983,16 +1344,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2.27</v>
+      </c>
       <c r="H18" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>8</v>
       </c>
-      <c r="I18" t="n">
+      <c r="N18" t="n">
         <v>7</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1013,16 +1395,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11.19</v>
+      </c>
       <c r="H19" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="N19" t="n">
         <v>6</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1043,16 +1446,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5.56</v>
+      </c>
       <c r="H20" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>7</v>
       </c>
-      <c r="I20" t="n">
+      <c r="N20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1073,16 +1497,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2.06</v>
+      </c>
       <c r="H21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1103,16 +1548,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>5.72</v>
+      </c>
       <c r="H22" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>10</v>
       </c>
-      <c r="I22" t="n">
+      <c r="N22" t="n">
         <v>9</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1133,16 +1599,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>9.18</v>
+      </c>
       <c r="H23" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="n">
+      <c r="N23" t="n">
         <v>6</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1163,16 +1650,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.37</v>
+      </c>
       <c r="H24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="N24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1193,16 +1701,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>7.14</v>
+      </c>
       <c r="H25" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="N25" t="n">
         <v>6</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1223,16 +1752,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1.28</v>
+      </c>
       <c r="H26" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>9</v>
       </c>
-      <c r="I26" t="n">
+      <c r="N26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1253,16 +1803,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>3.13</v>
+      </c>
       <c r="H27" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="N27" t="n">
         <v>3</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1283,16 +1854,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.7</v>
+      </c>
       <c r="H28" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="N28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1313,16 +1905,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1.44</v>
+      </c>
       <c r="H29" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>7</v>
       </c>
-      <c r="I29" t="n">
+      <c r="N29" t="n">
         <v>5</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1343,16 +1956,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2.56</v>
+      </c>
       <c r="H30" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>8</v>
       </c>
-      <c r="I30" t="n">
+      <c r="N30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1373,16 +2007,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.43</v>
+      </c>
       <c r="H31" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>10</v>
       </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1403,16 +2058,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>4.52</v>
+      </c>
       <c r="H32" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="N32" t="n">
         <v>6</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1433,16 +2109,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.76</v>
+      </c>
       <c r="H33" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>10</v>
       </c>
-      <c r="I33" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>7</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1463,16 +2160,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H34" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="I34" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>7</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1493,16 +2211,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2.06</v>
+      </c>
       <c r="H35" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="N35" t="n">
         <v>5</v>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1523,16 +2262,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2.28</v>
+      </c>
       <c r="H36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>6</v>
       </c>
-      <c r="I36" t="n">
+      <c r="N36" t="n">
         <v>7</v>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1553,16 +2313,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>5.41</v>
+      </c>
       <c r="H37" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>10</v>
       </c>
-      <c r="I37" t="n">
+      <c r="N37" t="n">
         <v>9</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1583,16 +2364,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1.76</v>
+      </c>
       <c r="H38" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="I38" t="n">
+      <c r="N38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1613,16 +2415,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2.81</v>
+      </c>
       <c r="H39" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="N39" t="n">
         <v>6</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1643,16 +2466,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1.14</v>
+      </c>
       <c r="H40" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="N40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1673,16 +2517,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>5.91</v>
+      </c>
       <c r="H41" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="n">
+      <c r="N41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1703,16 +2568,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H42" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
         <v>8</v>
       </c>
-      <c r="I42" t="n">
+      <c r="N42" t="n">
         <v>6</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1733,16 +2619,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>3.64</v>
+      </c>
       <c r="H43" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
         <v>7</v>
       </c>
-      <c r="I43" t="n">
+      <c r="N43" t="n">
         <v>6</v>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1763,16 +2670,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1.45</v>
+      </c>
       <c r="H44" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
         <v>5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="N44" t="n">
         <v>6</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1793,16 +2721,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>5.84</v>
+      </c>
       <c r="H45" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
         <v>5</v>
       </c>
-      <c r="I45" t="n">
+      <c r="N45" t="n">
         <v>7</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1823,16 +2772,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2.86</v>
+      </c>
       <c r="H46" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
         <v>6</v>
       </c>
-      <c r="I46" t="n">
+      <c r="N46" t="n">
         <v>6</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1853,16 +2823,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H47" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
         <v>2</v>
       </c>
-      <c r="I47" t="n">
+      <c r="N47" t="n">
         <v>4</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1883,16 +2874,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>11.22</v>
+      </c>
       <c r="H48" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
         <v>4</v>
       </c>
-      <c r="I48" t="n">
+      <c r="N48" t="n">
         <v>7</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1913,16 +2925,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H49" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
         <v>1.5</v>
       </c>
-      <c r="I49" t="n">
+      <c r="N49" t="n">
         <v>9</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1943,16 +2976,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>3.16</v>
+      </c>
       <c r="H50" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
         <v>4</v>
       </c>
-      <c r="I50" t="n">
+      <c r="N50" t="n">
         <v>8</v>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1973,16 +3027,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>5.59</v>
+      </c>
       <c r="H51" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
         <v>6</v>
       </c>
-      <c r="I51" t="n">
+      <c r="N51" t="n">
         <v>7</v>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2003,16 +3078,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.62</v>
+      </c>
       <c r="H52" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="n">
         <v>7</v>
       </c>
-      <c r="I52" t="n">
+      <c r="N52" t="n">
         <v>6</v>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2033,16 +3129,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>3.78</v>
+      </c>
       <c r="H53" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
         <v>5</v>
       </c>
-      <c r="I53" t="n">
+      <c r="N53" t="n">
         <v>6</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2063,16 +3180,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8</v>
+      </c>
       <c r="H54" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
         <v>9</v>
       </c>
-      <c r="I54" t="n">
+      <c r="N54" t="n">
         <v>7</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2093,16 +3231,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>5.28</v>
+      </c>
       <c r="H55" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="n">
         <v>6</v>
       </c>
-      <c r="I55" t="n">
+      <c r="N55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2123,16 +3282,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>5.28</v>
+      </c>
       <c r="H56" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
         <v>7</v>
       </c>
-      <c r="I56" t="n">
+      <c r="N56" t="n">
         <v>6</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2153,16 +3333,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1.86</v>
+      </c>
       <c r="H57" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="I57" t="n">
+      <c r="N57" t="n">
         <v>6</v>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2183,16 +3384,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1.7</v>
+      </c>
       <c r="H58" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="n">
         <v>5</v>
       </c>
-      <c r="I58" t="n">
+      <c r="N58" t="n">
         <v>6</v>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2213,16 +3435,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>3.07</v>
+      </c>
       <c r="H59" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="n">
         <v>10</v>
       </c>
-      <c r="I59" t="n">
+      <c r="N59" t="n">
         <v>10</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2243,16 +3486,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>4.69</v>
+      </c>
       <c r="H60" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="n">
         <v>1.5</v>
       </c>
-      <c r="I60" t="n">
+      <c r="N60" t="n">
         <v>5</v>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2273,16 +3537,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>8.65</v>
+      </c>
       <c r="H61" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="n">
         <v>10</v>
       </c>
-      <c r="I61" t="n">
+      <c r="N61" t="n">
         <v>10</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2303,16 +3588,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>7.78</v>
+      </c>
       <c r="H62" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
         <v>7</v>
       </c>
-      <c r="I62" t="n">
+      <c r="N62" t="n">
         <v>8</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2333,16 +3639,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
       <c r="H63" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="n">
         <v>7</v>
       </c>
-      <c r="I63" t="n">
+      <c r="N63" t="n">
         <v>8</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2363,16 +3690,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="H64" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
         <v>7</v>
       </c>
-      <c r="I64" t="n">
+      <c r="N64" t="n">
         <v>8</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2393,16 +3741,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>5.91</v>
+      </c>
       <c r="H65" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="n">
         <v>5</v>
       </c>
-      <c r="I65" t="n">
+      <c r="N65" t="n">
         <v>10</v>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2423,16 +3792,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H66" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
         <v>9</v>
       </c>
-      <c r="I66" t="n">
+      <c r="N66" t="n">
         <v>9</v>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2453,16 +3843,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
       <c r="H67" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="n">
         <v>6</v>
       </c>
-      <c r="I67" t="n">
+      <c r="N67" t="n">
         <v>7</v>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2483,16 +3894,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>4.39</v>
+      </c>
       <c r="H68" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
         <v>7</v>
       </c>
-      <c r="I68" t="n">
+      <c r="N68" t="n">
         <v>7</v>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2513,16 +3945,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>2.34</v>
+      </c>
       <c r="H69" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="n">
         <v>9</v>
       </c>
-      <c r="I69" t="n">
+      <c r="N69" t="n">
         <v>5</v>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2543,16 +3996,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>3.71</v>
+      </c>
       <c r="H70" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="n">
         <v>10</v>
       </c>
-      <c r="I70" t="n">
+      <c r="N70" t="n">
         <v>7</v>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2573,16 +4047,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1.16</v>
+      </c>
       <c r="H71" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="n">
         <v>10</v>
       </c>
-      <c r="I71" t="n">
+      <c r="N71" t="n">
         <v>8</v>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2603,16 +4098,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1.12</v>
+      </c>
       <c r="H72" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
         <v>3</v>
       </c>
-      <c r="I72" t="n">
+      <c r="N72" t="n">
         <v>9</v>
       </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2633,16 +4149,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>10.95</v>
+      </c>
       <c r="H73" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="n">
         <v>5</v>
       </c>
-      <c r="I73" t="n">
+      <c r="N73" t="n">
         <v>6</v>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2663,16 +4200,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>4.19</v>
+      </c>
       <c r="H74" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="n">
         <v>6</v>
       </c>
-      <c r="I74" t="n">
+      <c r="N74" t="n">
         <v>6</v>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2693,16 +4251,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H75" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="n">
         <v>7</v>
       </c>
-      <c r="I75" t="n">
+      <c r="N75" t="n">
         <v>9</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2723,16 +4302,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>5.4</v>
+      </c>
       <c r="H76" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="n">
         <v>9</v>
       </c>
-      <c r="I76" t="n">
+      <c r="N76" t="n">
         <v>8</v>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2753,16 +4353,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>7.09</v>
+      </c>
       <c r="H77" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="n">
         <v>9</v>
       </c>
-      <c r="I77" t="n">
+      <c r="N77" t="n">
         <v>8</v>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2783,16 +4404,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>6.15</v>
+      </c>
       <c r="H78" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="n">
         <v>3</v>
       </c>
-      <c r="I78" t="n">
+      <c r="N78" t="n">
         <v>6</v>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2813,16 +4455,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>4.45</v>
+      </c>
       <c r="H79" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
         <v>7</v>
       </c>
-      <c r="I79" t="n">
+      <c r="N79" t="n">
         <v>8</v>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2843,16 +4506,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1.48</v>
+      </c>
       <c r="H80" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
         <v>10</v>
       </c>
-      <c r="I80" t="n">
+      <c r="N80" t="n">
         <v>8</v>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2873,16 +4557,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>8.210000000000001</v>
+      </c>
       <c r="H81" t="n">
-        <v>13</v>
-      </c>
-      <c r="I81" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>6</v>
+      </c>
+      <c r="N81" t="n">
         <v>7</v>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2903,16 +4608,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>4.24</v>
+      </c>
       <c r="H82" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
         <v>6</v>
       </c>
-      <c r="I82" t="n">
+      <c r="N82" t="n">
         <v>6</v>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2933,16 +4659,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>8.16</v>
+      </c>
       <c r="H83" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
         <v>7</v>
       </c>
-      <c r="I83" t="n">
+      <c r="N83" t="n">
         <v>7</v>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2963,16 +4710,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>4.89</v>
+      </c>
       <c r="H84" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
         <v>7</v>
       </c>
-      <c r="I84" t="n">
+      <c r="N84" t="n">
         <v>7</v>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2993,16 +4761,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>3.55</v>
+      </c>
       <c r="H85" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
         <v>8</v>
       </c>
-      <c r="I85" t="n">
+      <c r="N85" t="n">
         <v>8</v>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3023,16 +4812,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>2.04</v>
+      </c>
       <c r="H86" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
         <v>9</v>
       </c>
-      <c r="I86" t="n">
+      <c r="N86" t="n">
         <v>8</v>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3053,16 +4863,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>4.45</v>
+      </c>
       <c r="H87" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
         <v>8</v>
       </c>
-      <c r="I87" t="n">
+      <c r="N87" t="n">
         <v>3</v>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3083,16 +4914,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1.4</v>
+      </c>
       <c r="H88" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
         <v>5</v>
       </c>
-      <c r="I88" t="n">
+      <c r="N88" t="n">
         <v>8</v>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3113,16 +4965,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="H89" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
         <v>3</v>
       </c>
-      <c r="I89" t="n">
+      <c r="N89" t="n">
         <v>6</v>
       </c>
-      <c r="J89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3143,16 +5016,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>3.92</v>
+      </c>
       <c r="H90" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
         <v>7</v>
       </c>
-      <c r="I90" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>7</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3173,16 +5067,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>5.27</v>
+      </c>
       <c r="H91" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
         <v>8</v>
       </c>
-      <c r="I91" t="n">
+      <c r="N91" t="n">
         <v>10</v>
       </c>
-      <c r="J91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3203,16 +5118,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H92" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
         <v>9</v>
       </c>
-      <c r="I92" t="n">
+      <c r="N92" t="n">
         <v>8</v>
       </c>
-      <c r="J92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3233,16 +5169,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>4.94</v>
+      </c>
       <c r="H93" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="n">
         <v>7</v>
       </c>
-      <c r="I93" t="n">
+      <c r="N93" t="n">
         <v>6</v>
       </c>
-      <c r="J93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3263,16 +5220,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>5.66</v>
+      </c>
       <c r="H94" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
         <v>9</v>
       </c>
-      <c r="I94" t="n">
+      <c r="N94" t="n">
         <v>8</v>
       </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3293,16 +5271,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0.6</v>
+      </c>
       <c r="H95" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="n">
         <v>6</v>
       </c>
-      <c r="I95" t="n">
+      <c r="N95" t="n">
         <v>6</v>
       </c>
-      <c r="J95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3323,16 +5322,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>3.3</v>
+      </c>
       <c r="H96" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="n">
         <v>10</v>
       </c>
-      <c r="I96" t="n">
+      <c r="N96" t="n">
         <v>8</v>
       </c>
-      <c r="J96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3353,16 +5373,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1.62</v>
+      </c>
       <c r="H97" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="n">
         <v>8</v>
       </c>
-      <c r="I97" t="n">
+      <c r="N97" t="n">
         <v>10</v>
       </c>
-      <c r="J97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3383,16 +5424,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>4.84</v>
+      </c>
       <c r="H98" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="n">
         <v>9</v>
       </c>
-      <c r="I98" t="n">
+      <c r="N98" t="n">
         <v>10</v>
       </c>
-      <c r="J98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3413,16 +5475,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>2.92</v>
+      </c>
       <c r="H99" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="n">
         <v>10</v>
       </c>
-      <c r="I99" t="n">
+      <c r="N99" t="n">
         <v>8</v>
       </c>
-      <c r="J99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3443,16 +5526,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H100" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="n">
         <v>3</v>
       </c>
-      <c r="I100" t="n">
+      <c r="N100" t="n">
         <v>6</v>
       </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3473,16 +5577,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>2.58</v>
+      </c>
       <c r="H101" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="n">
         <v>5</v>
       </c>
-      <c r="I101" t="n">
+      <c r="N101" t="n">
         <v>8</v>
       </c>
-      <c r="J101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3503,16 +5628,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H102" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="n">
         <v>10</v>
       </c>
-      <c r="I102" t="n">
+      <c r="N102" t="n">
         <v>10</v>
       </c>
-      <c r="J102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3533,16 +5679,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>5.07</v>
+      </c>
       <c r="H103" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="n">
         <v>9</v>
       </c>
-      <c r="I103" t="n">
+      <c r="N103" t="n">
         <v>8</v>
       </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3563,16 +5730,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>5.46</v>
+      </c>
       <c r="H104" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
         <v>8</v>
       </c>
-      <c r="I104" t="n">
+      <c r="N104" t="n">
         <v>6</v>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3593,16 +5781,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0.52</v>
+      </c>
       <c r="H105" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="n">
         <v>9</v>
       </c>
-      <c r="I105" t="n">
+      <c r="N105" t="n">
         <v>10</v>
       </c>
-      <c r="J105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3623,16 +5832,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0.48</v>
+      </c>
       <c r="H106" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="n">
         <v>5</v>
       </c>
-      <c r="I106" t="n">
-        <v>8</v>
-      </c>
-      <c r="J106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>7</v>
+      </c>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3653,16 +5883,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>3.08</v>
+      </c>
       <c r="H107" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="n">
         <v>2</v>
       </c>
-      <c r="I107" t="n">
+      <c r="N107" t="n">
         <v>6</v>
       </c>
-      <c r="J107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3683,16 +5934,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>3.98</v>
+      </c>
       <c r="H108" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="n">
         <v>6</v>
       </c>
-      <c r="I108" t="n">
+      <c r="N108" t="n">
         <v>8</v>
       </c>
-      <c r="J108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3713,16 +5985,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>2.66</v>
+      </c>
       <c r="H109" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="n">
         <v>10</v>
       </c>
-      <c r="I109" t="n">
-        <v>8</v>
-      </c>
-      <c r="J109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3743,16 +6036,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0.91</v>
+      </c>
       <c r="H110" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
         <v>6</v>
       </c>
-      <c r="I110" t="n">
+      <c r="N110" t="n">
         <v>6</v>
       </c>
-      <c r="J110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3773,16 +6087,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0.21</v>
+      </c>
       <c r="H111" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="n">
         <v>10</v>
       </c>
-      <c r="I111" t="n">
+      <c r="N111" t="n">
         <v>8</v>
       </c>
-      <c r="J111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3803,16 +6138,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H112" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
         <v>5</v>
       </c>
-      <c r="I112" t="n">
+      <c r="N112" t="n">
         <v>6</v>
       </c>
-      <c r="J112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3833,16 +6189,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H113" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
         <v>3</v>
       </c>
-      <c r="I113" t="n">
+      <c r="N113" t="n">
         <v>5</v>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3863,16 +6240,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1.35</v>
+      </c>
       <c r="H114" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
         <v>7</v>
       </c>
-      <c r="I114" t="n">
+      <c r="N114" t="n">
         <v>8</v>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3893,16 +6291,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0.58</v>
+      </c>
       <c r="H115" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
         <v>3</v>
       </c>
-      <c r="I115" t="n">
-        <v>11</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>7</v>
+      </c>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3923,16 +6342,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H116" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
         <v>7</v>
       </c>
-      <c r="I116" t="n">
+      <c r="N116" t="n">
         <v>6</v>
       </c>
-      <c r="J116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3953,16 +6393,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1.06</v>
+      </c>
       <c r="H117" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
         <v>9</v>
       </c>
-      <c r="I117" t="n">
+      <c r="N117" t="n">
         <v>10</v>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3983,16 +6444,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1.06</v>
+      </c>
       <c r="H118" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
         <v>7</v>
       </c>
-      <c r="I118" t="n">
+      <c r="N118" t="n">
         <v>7</v>
       </c>
-      <c r="J118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4013,16 +6495,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3.59</v>
+      </c>
       <c r="H119" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
         <v>8</v>
       </c>
-      <c r="I119" t="n">
+      <c r="N119" t="n">
         <v>7</v>
       </c>
-      <c r="J119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4043,16 +6546,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>5.3</v>
+      </c>
       <c r="H120" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
         <v>7</v>
       </c>
-      <c r="I120" t="n">
+      <c r="N120" t="n">
         <v>9</v>
       </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4073,16 +6597,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>4.97</v>
+      </c>
       <c r="H121" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
         <v>9</v>
       </c>
-      <c r="I121" t="n">
+      <c r="N121" t="n">
         <v>9</v>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4103,16 +6648,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>6.93</v>
+      </c>
       <c r="H122" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
         <v>5</v>
       </c>
-      <c r="I122" t="n">
+      <c r="N122" t="n">
         <v>5</v>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4133,16 +6699,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>5.46</v>
+      </c>
       <c r="H123" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
         <v>6</v>
       </c>
-      <c r="I123" t="n">
+      <c r="N123" t="n">
         <v>10</v>
       </c>
-      <c r="J123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4163,16 +6750,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0.31</v>
+      </c>
       <c r="H124" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
         <v>6</v>
       </c>
-      <c r="I124" t="n">
+      <c r="N124" t="n">
         <v>7</v>
       </c>
-      <c r="J124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4193,16 +6801,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>5.17</v>
+      </c>
       <c r="H125" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
         <v>1.5</v>
       </c>
-      <c r="I125" t="n">
+      <c r="N125" t="n">
         <v>3</v>
       </c>
-      <c r="J125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4223,16 +6852,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>6.16</v>
+      </c>
       <c r="H126" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
         <v>7</v>
       </c>
-      <c r="I126" t="n">
+      <c r="N126" t="n">
         <v>8</v>
       </c>
-      <c r="J126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4253,16 +6903,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1.1</v>
+      </c>
       <c r="H127" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
         <v>10</v>
       </c>
-      <c r="I127" t="n">
+      <c r="N127" t="n">
         <v>8</v>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4283,16 +6954,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H128" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
         <v>7</v>
       </c>
-      <c r="I128" t="n">
+      <c r="N128" t="n">
         <v>6</v>
       </c>
-      <c r="J128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4313,16 +7005,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H129" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
         <v>6</v>
       </c>
-      <c r="I129" t="n">
+      <c r="N129" t="n">
         <v>7</v>
       </c>
-      <c r="J129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4343,16 +7056,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H130" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
         <v>3</v>
       </c>
-      <c r="I130" t="n">
+      <c r="N130" t="n">
         <v>5</v>
       </c>
-      <c r="J130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4373,16 +7107,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2.25</v>
+      </c>
       <c r="H131" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
         <v>8</v>
       </c>
-      <c r="I131" t="n">
+      <c r="N131" t="n">
         <v>8</v>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4403,16 +7158,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>4.25</v>
+      </c>
       <c r="H132" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
         <v>8</v>
       </c>
-      <c r="I132" t="n">
+      <c r="N132" t="n">
         <v>3</v>
       </c>
-      <c r="J132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4433,16 +7209,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3</v>
+      </c>
       <c r="H133" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
         <v>6</v>
       </c>
-      <c r="I133" t="n">
+      <c r="N133" t="n">
         <v>10</v>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4463,16 +7260,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>4.64</v>
+      </c>
       <c r="H134" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
         <v>7</v>
       </c>
-      <c r="I134" t="n">
+      <c r="N134" t="n">
         <v>6</v>
       </c>
-      <c r="J134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4493,16 +7311,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="H135" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
         <v>9</v>
       </c>
-      <c r="I135" t="n">
+      <c r="N135" t="n">
         <v>8</v>
       </c>
-      <c r="J135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4523,16 +7362,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H136" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
         <v>7</v>
       </c>
-      <c r="I136" t="n">
+      <c r="N136" t="n">
         <v>8</v>
       </c>
-      <c r="J136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4553,16 +7413,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0.78</v>
+      </c>
       <c r="H137" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
         <v>9</v>
       </c>
-      <c r="I137" t="n">
+      <c r="N137" t="n">
         <v>7</v>
       </c>
-      <c r="J137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4583,16 +7464,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0.38</v>
+      </c>
       <c r="H138" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
         <v>6</v>
       </c>
-      <c r="I138" t="n">
+      <c r="N138" t="n">
         <v>8</v>
       </c>
-      <c r="J138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4613,16 +7515,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1.63</v>
+      </c>
       <c r="H139" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
         <v>9</v>
       </c>
-      <c r="I139" t="n">
+      <c r="N139" t="n">
         <v>8</v>
       </c>
-      <c r="J139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4643,16 +7566,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>6.35</v>
+      </c>
       <c r="H140" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
         <v>6</v>
       </c>
-      <c r="I140" t="n">
+      <c r="N140" t="n">
         <v>8</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4673,16 +7617,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1.31</v>
+      </c>
       <c r="H141" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="n">
         <v>7</v>
       </c>
-      <c r="I141" t="n">
+      <c r="N141" t="n">
         <v>10</v>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4703,16 +7668,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>2.54</v>
+      </c>
       <c r="H142" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
         <v>7</v>
       </c>
-      <c r="I142" t="n">
+      <c r="N142" t="n">
         <v>8</v>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4733,16 +7719,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>3.86</v>
+      </c>
       <c r="H143" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
         <v>7</v>
       </c>
-      <c r="I143" t="n">
+      <c r="N143" t="n">
         <v>7</v>
       </c>
-      <c r="J143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4763,16 +7770,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>8.99</v>
+      </c>
       <c r="H144" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
         <v>9</v>
       </c>
-      <c r="I144" t="n">
+      <c r="N144" t="n">
         <v>8</v>
       </c>
-      <c r="J144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4793,16 +7821,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2.58</v>
+      </c>
       <c r="H145" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="n">
         <v>7</v>
       </c>
-      <c r="I145" t="n">
+      <c r="N145" t="n">
         <v>9</v>
       </c>
-      <c r="J145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4823,16 +7872,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>4.88</v>
+      </c>
       <c r="H146" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
         <v>7</v>
       </c>
-      <c r="I146" t="n">
+      <c r="N146" t="n">
         <v>8</v>
       </c>
-      <c r="J146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4853,16 +7923,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>4.64</v>
+      </c>
       <c r="H147" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
         <v>10</v>
       </c>
-      <c r="I147" t="n">
+      <c r="N147" t="n">
         <v>9</v>
       </c>
-      <c r="J147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4883,16 +7974,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>3.81</v>
+      </c>
       <c r="H148" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
         <v>6</v>
       </c>
-      <c r="I148" t="n">
+      <c r="N148" t="n">
         <v>7</v>
       </c>
-      <c r="J148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4913,16 +8025,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>5.17</v>
+      </c>
       <c r="H149" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="n">
         <v>8</v>
       </c>
-      <c r="I149" t="n">
+      <c r="N149" t="n">
         <v>9</v>
       </c>
-      <c r="J149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4943,16 +8076,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H150" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
         <v>3</v>
       </c>
-      <c r="I150" t="n">
+      <c r="N150" t="n">
         <v>6</v>
       </c>
-      <c r="J150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4973,16 +8127,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>4.42</v>
+      </c>
       <c r="H151" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
         <v>7</v>
       </c>
-      <c r="I151" t="n">
+      <c r="N151" t="n">
         <v>10</v>
       </c>
-      <c r="J151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5003,16 +8178,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1.22</v>
+      </c>
       <c r="H152" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
         <v>8</v>
       </c>
-      <c r="I152" t="n">
+      <c r="N152" t="n">
         <v>6</v>
       </c>
-      <c r="J152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5033,16 +8229,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1.28</v>
+      </c>
       <c r="H153" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
         <v>5</v>
       </c>
-      <c r="I153" t="n">
+      <c r="N153" t="n">
         <v>6</v>
       </c>
-      <c r="J153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5063,16 +8280,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>4.31</v>
+      </c>
       <c r="H154" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
         <v>10</v>
       </c>
-      <c r="I154" t="n">
+      <c r="N154" t="n">
         <v>8</v>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5093,16 +8331,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H155" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
         <v>6</v>
       </c>
-      <c r="I155" t="n">
+      <c r="N155" t="n">
         <v>8</v>
       </c>
-      <c r="J155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5123,16 +8382,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0.71</v>
+      </c>
       <c r="H156" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="n">
         <v>9</v>
       </c>
-      <c r="I156" t="n">
+      <c r="N156" t="n">
         <v>6</v>
       </c>
-      <c r="J156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5153,16 +8433,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>5.18</v>
+      </c>
       <c r="H157" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
         <v>7</v>
       </c>
-      <c r="I157" t="n">
+      <c r="N157" t="n">
         <v>4</v>
       </c>
-      <c r="J157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5183,16 +8484,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>5.33</v>
+      </c>
       <c r="H158" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
         <v>9</v>
       </c>
-      <c r="I158" t="n">
+      <c r="N158" t="n">
         <v>6</v>
       </c>
-      <c r="J158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5213,16 +8535,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H159" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="n">
         <v>9</v>
       </c>
-      <c r="I159" t="n">
+      <c r="N159" t="n">
         <v>6</v>
       </c>
-      <c r="J159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5243,16 +8586,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>4.71</v>
+      </c>
       <c r="H160" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="n">
         <v>8</v>
       </c>
-      <c r="I160" t="n">
+      <c r="N160" t="n">
         <v>9</v>
       </c>
-      <c r="J160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5273,16 +8637,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1.79</v>
+      </c>
       <c r="H161" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="n">
         <v>6</v>
       </c>
-      <c r="I161" t="n">
+      <c r="N161" t="n">
         <v>8</v>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5303,16 +8688,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0.89</v>
+      </c>
       <c r="H162" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="n">
         <v>7</v>
       </c>
-      <c r="I162" t="n">
+      <c r="N162" t="n">
         <v>5</v>
       </c>
-      <c r="J162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5333,16 +8739,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1.26</v>
+      </c>
       <c r="H163" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="n">
         <v>8</v>
       </c>
-      <c r="I163" t="n">
+      <c r="N163" t="n">
         <v>7</v>
       </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5363,16 +8790,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0.38</v>
+      </c>
       <c r="H164" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="n">
         <v>6</v>
       </c>
-      <c r="I164" t="n">
+      <c r="N164" t="n">
         <v>8</v>
       </c>
-      <c r="J164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5393,16 +8841,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0.77</v>
+      </c>
       <c r="H165" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="n">
         <v>10</v>
       </c>
-      <c r="I165" t="n">
+      <c r="N165" t="n">
         <v>7</v>
       </c>
-      <c r="J165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5423,16 +8892,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>5.25</v>
+      </c>
       <c r="H166" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
         <v>10</v>
       </c>
-      <c r="I166" t="n">
+      <c r="N166" t="n">
         <v>8</v>
       </c>
-      <c r="J166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5453,16 +8943,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1.27</v>
+      </c>
       <c r="H167" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="n">
         <v>8</v>
       </c>
-      <c r="I167" t="n">
+      <c r="N167" t="n">
         <v>9</v>
       </c>
-      <c r="J167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5483,16 +8994,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0.51</v>
+      </c>
       <c r="H168" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
         <v>3</v>
       </c>
-      <c r="I168" t="n">
+      <c r="N168" t="n">
         <v>5</v>
       </c>
-      <c r="J168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5513,16 +9045,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>2.78</v>
+      </c>
       <c r="H169" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
         <v>9</v>
       </c>
-      <c r="I169" t="n">
+      <c r="N169" t="n">
         <v>8</v>
       </c>
-      <c r="J169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5543,16 +9096,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>5.61</v>
+      </c>
       <c r="H170" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
         <v>2</v>
       </c>
-      <c r="I170" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>7</v>
+      </c>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5573,16 +9147,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>4.49</v>
+      </c>
       <c r="H171" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
         <v>8</v>
       </c>
-      <c r="I171" t="n">
+      <c r="N171" t="n">
         <v>10</v>
       </c>
-      <c r="J171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5603,16 +9198,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0.89</v>
+      </c>
       <c r="H172" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="n">
         <v>9</v>
       </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" t="inlineStr"/>
+      <c r="N172" t="n">
+        <v>7</v>
+      </c>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5633,16 +9249,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>1.03</v>
+      </c>
       <c r="H173" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
         <v>6</v>
       </c>
-      <c r="I173" t="n">
+      <c r="N173" t="n">
         <v>5</v>
       </c>
-      <c r="J173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5663,16 +9300,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H174" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="n">
         <v>9</v>
       </c>
-      <c r="I174" t="n">
+      <c r="N174" t="n">
         <v>8</v>
       </c>
-      <c r="J174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5693,16 +9351,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>0.31</v>
+      </c>
       <c r="H175" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="n">
         <v>4</v>
       </c>
-      <c r="I175" t="n">
+      <c r="N175" t="n">
         <v>5</v>
       </c>
-      <c r="J175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5723,16 +9402,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1.41</v>
+      </c>
       <c r="H176" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="n">
         <v>5</v>
       </c>
-      <c r="I176" t="n">
+      <c r="N176" t="n">
         <v>9</v>
       </c>
-      <c r="J176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5753,16 +9453,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>10.88</v>
+      </c>
       <c r="H177" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="n">
         <v>7</v>
       </c>
-      <c r="I177" t="n">
+      <c r="N177" t="n">
         <v>7</v>
       </c>
-      <c r="J177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5783,16 +9504,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>3.66</v>
+      </c>
       <c r="H178" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="n">
         <v>8</v>
       </c>
-      <c r="I178" t="n">
-        <v>8</v>
-      </c>
-      <c r="J178" t="inlineStr"/>
+      <c r="N178" t="n">
+        <v>7</v>
+      </c>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5813,16 +9555,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1.38</v>
+      </c>
       <c r="H179" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="n">
         <v>9</v>
       </c>
-      <c r="I179" t="n">
+      <c r="N179" t="n">
         <v>9</v>
       </c>
-      <c r="J179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5843,16 +9606,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>11.48</v>
+      </c>
       <c r="H180" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="n">
         <v>9</v>
       </c>
-      <c r="I180" t="n">
+      <c r="N180" t="n">
         <v>8</v>
       </c>
-      <c r="J180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5873,16 +9657,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>5.4</v>
+      </c>
       <c r="H181" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="n">
         <v>7</v>
       </c>
-      <c r="I181" t="n">
+      <c r="N181" t="n">
         <v>6</v>
       </c>
-      <c r="J181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5903,16 +9708,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>3.25</v>
+      </c>
       <c r="H182" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="n">
         <v>3</v>
       </c>
-      <c r="I182" t="n">
+      <c r="N182" t="n">
         <v>6</v>
       </c>
-      <c r="J182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5933,16 +9759,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>11.73375</v>
+      </c>
       <c r="H183" t="n">
+        <v>24.15125</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="n">
         <v>7</v>
       </c>
-      <c r="I183" t="n">
+      <c r="N183" t="n">
         <v>8</v>
       </c>
-      <c r="J183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5963,16 +9810,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>6.55</v>
+      </c>
       <c r="H184" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="n">
         <v>7</v>
       </c>
-      <c r="I184" t="n">
+      <c r="N184" t="n">
         <v>9</v>
       </c>
-      <c r="J184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5993,16 +9861,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>4.71</v>
+      </c>
       <c r="H185" t="n">
+        <v>19</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="n">
         <v>8</v>
       </c>
-      <c r="I185" t="n">
+      <c r="N185" t="n">
         <v>9</v>
       </c>
-      <c r="J185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6023,16 +9912,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>1.19</v>
+      </c>
       <c r="H186" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="n">
         <v>6</v>
       </c>
-      <c r="I186" t="n">
+      <c r="N186" t="n">
         <v>9</v>
       </c>
-      <c r="J186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6053,16 +9963,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>5.65</v>
+      </c>
       <c r="H187" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="n">
         <v>9</v>
       </c>
-      <c r="I187" t="n">
+      <c r="N187" t="n">
         <v>8</v>
       </c>
-      <c r="J187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6083,16 +10014,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>0.95</v>
+      </c>
       <c r="H188" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="n">
         <v>3</v>
       </c>
-      <c r="I188" t="n">
+      <c r="N188" t="n">
         <v>6</v>
       </c>
-      <c r="J188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6113,16 +10065,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>2.24</v>
+      </c>
       <c r="H189" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="n">
         <v>3</v>
       </c>
-      <c r="I189" t="n">
+      <c r="N189" t="n">
         <v>6</v>
       </c>
-      <c r="J189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6143,16 +10116,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>4.14</v>
+      </c>
       <c r="H190" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="n">
         <v>8</v>
       </c>
-      <c r="I190" t="n">
+      <c r="N190" t="n">
         <v>3</v>
       </c>
-      <c r="J190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6173,16 +10167,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>2.01</v>
+      </c>
       <c r="H191" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="n">
         <v>7</v>
       </c>
-      <c r="I191" t="n">
+      <c r="N191" t="n">
         <v>8</v>
       </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6203,16 +10218,37 @@
           <t>PARCEL_PREMIUM</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>11.43</v>
+      </c>
       <c r="H192" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="n">
         <v>6</v>
       </c>
-      <c r="I192" t="n">
+      <c r="N192" t="n">
         <v>8</v>
       </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6233,16 +10269,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>5.14</v>
+      </c>
       <c r="H193" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="n">
         <v>3</v>
       </c>
-      <c r="I193" t="n">
+      <c r="N193" t="n">
         <v>10</v>
       </c>
-      <c r="J193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6263,16 +10320,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>5.79</v>
+      </c>
       <c r="H194" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
         <v>5</v>
       </c>
-      <c r="I194" t="n">
+      <c r="N194" t="n">
         <v>6</v>
       </c>
-      <c r="J194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6293,16 +10371,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="H195" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
         <v>6</v>
       </c>
-      <c r="I195" t="n">
+      <c r="N195" t="n">
         <v>6</v>
       </c>
-      <c r="J195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6323,16 +10422,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>0.62</v>
+      </c>
       <c r="H196" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
         <v>10</v>
       </c>
-      <c r="I196" t="n">
+      <c r="N196" t="n">
         <v>10</v>
       </c>
-      <c r="J196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6353,16 +10473,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>1.46</v>
+      </c>
       <c r="H197" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="n">
         <v>3</v>
       </c>
-      <c r="I197" t="n">
+      <c r="N197" t="n">
         <v>10</v>
       </c>
-      <c r="J197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6383,16 +10524,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1.38</v>
+      </c>
       <c r="H198" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="n">
         <v>8</v>
       </c>
-      <c r="I198" t="n">
+      <c r="N198" t="n">
         <v>8</v>
       </c>
-      <c r="J198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6413,16 +10575,37 @@
           <t>PARCEL_EXPRESS</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>4.63</v>
+      </c>
       <c r="H199" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
         <v>9</v>
       </c>
-      <c r="I199" t="n">
+      <c r="N199" t="n">
         <v>8</v>
       </c>
-      <c r="J199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6443,16 +10626,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>2.57</v>
+      </c>
       <c r="H200" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="n">
         <v>6</v>
       </c>
-      <c r="I200" t="n">
+      <c r="N200" t="n">
         <v>6</v>
       </c>
-      <c r="J200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6473,16 +10677,37 @@
           <t>PARCEL_STANDARD</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H201" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
         <v>6</v>
       </c>
-      <c r="I201" t="n">
+      <c r="N201" t="n">
         <v>7</v>
       </c>
-      <c r="J201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
